--- a/branches/Richard-FHIR-R5/observations-summary.xlsx
+++ b/branches/Richard-FHIR-R5/observations-summary.xlsx
@@ -101,7 +101,7 @@
     <t>dateTime</t>
   </si>
   <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period, Attachment, Reference</t>
   </si>
 </sst>
 </file>

--- a/branches/Richard-FHIR-R5/observations-summary.xlsx
+++ b/branches/Richard-FHIR-R5/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
   <si>
     <t>Profile</t>
   </si>
@@ -47,15 +47,36 @@
     <t>Method</t>
   </si>
   <si>
+    <t>art-initiated</t>
+  </si>
+  <si>
+    <t>ART Initiated</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>null#47241-5</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period, Attachment, Reference</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
     <t>hiv-arv-adherence</t>
   </si>
   <si>
     <t>Patient's Adherence to ARV Treatment</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>SNOMED CT#386091000</t>
   </si>
   <si>
@@ -65,9 +86,6 @@
     <t>CodeableConcept</t>
   </si>
   <si>
-    <t>optional</t>
-  </si>
-  <si>
     <t>hiv-patient-breastfeeding</t>
   </si>
   <si>
@@ -96,12 +114,6 @@
   </si>
   <si>
     <t>SNOMED CT#250421003</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period, Attachment, Reference</t>
   </si>
 </sst>
 </file>
@@ -235,7 +247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -290,16 +302,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s" s="2">
         <v>13</v>
@@ -310,31 +322,31 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="J3" t="s" s="2">
         <v>13</v>
@@ -345,31 +357,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>15</v>
-      </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s" s="2">
         <v>13</v>
@@ -380,10 +392,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>13</v>
@@ -392,24 +404,59 @@
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="F5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>29</v>
-      </c>
       <c r="I5" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="J5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s" s="2">
+      <c r="I6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>13</v>
       </c>
     </row>
